--- a/education_forms/044_hiragana_recognition_quiz--education_forms.xlsx
+++ b/education_forms/044_hiragana_recognition_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -776,11 +776,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -826,19 +826,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hiragana_quiz_responses_choices</t>
+          <t>hiragana_quiz_confidence_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,19 +860,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hiragana_quiz_confidence_choices</t>
+          <t>teacher_comments_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -889,68 +889,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hiragana_quiz_confidence_choices</t>
+          <t>teacher_comments_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>teacher_comments_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>teacher_comments_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>teacher_comments_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
